--- a/jira_export_2026-08-26.xlsx
+++ b/jira_export_2026-08-26.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>21,987 €</t>
+          <t>25,876 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>9,838 €</t>
+          <t>13,727 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>400 h</t>
+          <t>402 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,7 +886,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="L6" s="14" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L10" s="14" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="P11" s="12" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -2090,9 +2090,9 @@
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>495</v>
-      </c>
-      <c r="O19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P19" s="12" t="n">
@@ -2221,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>4424</v>
+        <v>3602.4</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>821.6</v>
@@ -6097,10 +6097,10 @@
         <v>0</v>
       </c>
       <c r="O75" s="12" t="n">
-        <v>0</v>
+        <v>109.972</v>
       </c>
       <c r="P75" s="12" t="n">
-        <v>0</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -6721,7 +6721,7 @@
         <v>6</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
@@ -6737,10 +6737,10 @@
         <v>416.475</v>
       </c>
       <c r="O84" s="16" t="n">
-        <v>0</v>
+        <v>138.825</v>
       </c>
       <c r="P84" s="15" t="n">
-        <v>0</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="85">
@@ -7241,10 +7241,10 @@
         <v>690</v>
       </c>
       <c r="O91" s="16" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="P91" s="12" t="n">
-        <v>0</v>
+        <v>26.29</v>
       </c>
     </row>
     <row r="92">
@@ -7385,10 +7385,10 @@
         <v>0</v>
       </c>
       <c r="O93" s="12" t="n">
-        <v>0</v>
+        <v>224.05</v>
       </c>
       <c r="P93" s="12" t="n">
-        <v>0</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -7457,10 +7457,10 @@
         <v>187.5</v>
       </c>
       <c r="O94" s="16" t="n">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="P94" s="15" t="n">
-        <v>0</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="95">
@@ -7529,10 +7529,10 @@
         <v>787.5</v>
       </c>
       <c r="O95" s="16" t="n">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="P95" s="12" t="n">
-        <v>0</v>
+        <v>108.62</v>
       </c>
     </row>
     <row r="96">
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="O98" s="15" t="n">
-        <v>0</v>
+        <v>1351.26</v>
       </c>
       <c r="P98" s="15" t="n">
-        <v>0</v>
+        <v>675.63</v>
       </c>
     </row>
     <row r="99">
@@ -8241,10 +8241,10 @@
         <v>0</v>
       </c>
       <c r="O105" s="12" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="P105" s="12" t="n">
-        <v>0</v>
+        <v>155.15</v>
       </c>
     </row>
     <row r="106">
@@ -9597,7 +9597,7 @@
         <v>20</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="L125" s="11" t="inlineStr"/>
       <c r="M125" s="11" t="inlineStr"/>
@@ -10659,7 +10659,7 @@
         <v>3</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L142" s="14" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>595.7</v>
       </c>
       <c r="P142" s="15" t="n">
-        <v>0</v>
+        <v>1191.4</v>
       </c>
     </row>
     <row r="143">
@@ -10804,13 +10804,13 @@
       <c r="L145" s="17" t="inlineStr"/>
       <c r="M145" s="17" t="inlineStr"/>
       <c r="N145" s="18" t="n">
-        <v>64017.394</v>
+        <v>62700.79400000001</v>
       </c>
       <c r="O145" s="18" t="n">
-        <v>21986.73</v>
+        <v>25875.837</v>
       </c>
       <c r="P145" s="18" t="n">
-        <v>101.2</v>
+        <v>117.88</v>
       </c>
     </row>
   </sheetData>
@@ -11659,16 +11659,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>160.25</v>
+        <v>161.75</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>30.5</v>
+        <v>30.75</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>10.75</v>
+        <v>11.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>201.5</v>
+        <v>203.75</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>66.25</v>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.9%</t>
         </is>
       </c>
     </row>
@@ -11805,16 +11805,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>375387</v>
+        <v>371498</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>142446</v>
+        <v>139336</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>232941</v>
+        <v>232162</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>146396</v>
+        <v>145617</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -11830,16 +11830,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>167245</v>
+        <v>163355</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>63615</v>
+        <v>60505</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>103630</v>
+        <v>102851</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>86439</v>
+        <v>85660</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>11307</v>
@@ -12619,7 +12619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -12640,7 +12640,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6 clôture(s) : 6 projet(s), 0 rework</t>
+          <t>7 clôture(s) : 7 projet(s), 0 rework</t>
         </is>
       </c>
     </row>
@@ -12857,32 +12857,62 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34966</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>[Commune de Villeneuve D'Ascq] - Ajout de 5 licences supplém</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Commune de Villeneuve D'Ascq</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n">
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n">
         <v>0</v>
       </c>
     </row>

--- a/jira_export_2026-08-26.xlsx
+++ b/jira_export_2026-08-26.xlsx
@@ -226,7 +226,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -286,6 +286,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -815,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>402 h</t>
+          <t>403 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -886,21 +889,21 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
       <c r="C25" s="7" t="n"/>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="E25" s="7" t="n"/>
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -916,7 +919,7 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
@@ -933,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P145"/>
+  <dimension ref="A1:P146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1301,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1320,7 +1323,7 @@
         <v>750</v>
       </c>
       <c r="P8" s="15" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -1386,9 +1389,9 @@
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="12" t="n">
+        <v>1100</v>
+      </c>
+      <c r="O9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P9" s="12" t="n">
@@ -3645,7 +3648,7 @@
         <v>2</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
@@ -3664,7 +3667,7 @@
         <v>438.2</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>48.69</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="42">
@@ -7322,12 +7325,12 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7337,12 +7340,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -7362,33 +7365,33 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>2.42</v>
+        <v>0.25</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O93" s="12" t="n">
-        <v>224.05</v>
+        <v>0</v>
       </c>
       <c r="P93" s="12" t="n">
-        <v>92.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -7445,22 +7448,22 @@
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O94" s="16" t="n">
-        <v>62.5</v>
+        <v>0</v>
+      </c>
+      <c r="O94" s="15" t="n">
+        <v>224.05</v>
       </c>
       <c r="P94" s="15" t="n">
-        <v>25.86</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="95">
@@ -7517,47 +7520,49 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O95" s="16" t="n">
-        <v>262.5</v>
+        <v>62.5</v>
       </c>
       <c r="P95" s="12" t="n">
-        <v>108.62</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E96" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
@@ -7576,64 +7581,62 @@
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0.5</v>
+        <v>2.42</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="15" t="n">
-        <v>0</v>
+        <v>787.5</v>
+      </c>
+      <c r="O96" s="16" t="n">
+        <v>262.5</v>
       </c>
       <c r="P96" s="15" t="n">
-        <v>0</v>
+        <v>108.62</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v/>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -7643,34 +7646,34 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>725</v>
-      </c>
-      <c r="O97" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7680,30 +7683,32 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E98" s="14" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -7713,49 +7718,49 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" s="15" t="n">
-        <v>1351.26</v>
+        <v>725</v>
+      </c>
+      <c r="O98" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P98" s="15" t="n">
-        <v>675.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7765,13 +7770,11 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E99" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v/>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
@@ -7790,33 +7793,33 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>1.05</v>
+        <v>2</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O99" s="12" t="n">
-        <v>0</v>
+        <v>1351.26</v>
       </c>
       <c r="P99" s="12" t="n">
-        <v>0</v>
+        <v>675.63</v>
       </c>
     </row>
     <row r="100">
@@ -7873,12 +7876,12 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
@@ -7945,12 +7948,12 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
@@ -8017,12 +8020,12 @@
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
@@ -8089,18 +8092,18 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O103" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="12" t="n">
@@ -8110,12 +8113,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
@@ -8125,11 +8128,13 @@
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E104" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E104" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
@@ -8143,34 +8148,34 @@
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>4.25</v>
+        <v>1.05</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O104" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8180,12 +8185,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8195,7 +8200,7 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8213,49 +8218,49 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>8.25</v>
+        <v>4.25</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O105" s="12" t="n">
-        <v>1280</v>
+        <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
-        <v>155.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
@@ -8265,7 +8270,7 @@
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8288,60 +8293,58 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>1.5</v>
+        <v>8.25</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O106" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O106" s="15" t="n">
+        <v>1280</v>
       </c>
       <c r="P106" s="15" t="n">
-        <v>0</v>
+        <v>155.15</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v/>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
@@ -8360,29 +8363,29 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O107" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O107" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8392,27 +8395,27 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
@@ -8422,27 +8425,35 @@
       </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H108" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" s="14" t="inlineStr"/>
-      <c r="M108" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L108" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M108" s="14" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N108" s="15" t="n">
         <v>0</v>
       </c>
@@ -8456,26 +8467,28 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
@@ -8484,35 +8497,27 @@
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L109" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M109" s="11" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr"/>
+      <c r="M109" s="11" t="inlineStr"/>
       <c r="N109" s="12" t="n">
         <v>0</v>
       </c>
@@ -8575,12 +8580,12 @@
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
@@ -8596,22 +8601,22 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -8634,23 +8639,23 @@
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8666,12 +8671,12 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -8681,7 +8686,7 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8704,23 +8709,23 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
@@ -8736,12 +8741,12 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -8751,7 +8756,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8774,23 +8779,23 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
         <v>13</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
@@ -8855,12 +8860,12 @@
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
@@ -8891,7 +8896,7 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8925,12 +8930,12 @@
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
@@ -8961,7 +8966,7 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -8995,12 +9000,12 @@
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
@@ -9016,22 +9021,22 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9049,34 +9054,34 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K117" s="11" t="n">
-        <v>0.5</v>
+        <v>1.31</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O117" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9086,22 +9091,22 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9117,24 +9122,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H118" s="14" t="inlineStr"/>
+      <c r="H118" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K118" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="L118" s="14" t="inlineStr"/>
-      <c r="M118" s="14" t="inlineStr"/>
+      <c r="L118" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M118" s="14" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N118" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O118" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O118" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="15" t="n">
@@ -9144,22 +9161,22 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9175,11 +9192,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H119" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H119" s="11" t="inlineStr"/>
       <c r="I119" s="11" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -9189,18 +9202,10 @@
         <v>16</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="L119" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M119" s="11" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L119" s="11" t="inlineStr"/>
+      <c r="M119" s="11" t="inlineStr"/>
       <c r="N119" s="12" t="n">
         <v>0</v>
       </c>
@@ -9214,22 +9219,22 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9247,28 +9252,28 @@
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
         <v>16</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
@@ -9284,22 +9289,22 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9322,29 +9327,29 @@
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K121" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O121" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
@@ -9354,22 +9359,22 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9382,27 +9387,39 @@
       </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H122" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H122" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L122" s="14" t="inlineStr"/>
-      <c r="M122" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L122" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M122" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N122" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O122" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="15" t="n">
@@ -9412,22 +9429,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9440,35 +9457,23 @@
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H123" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr"/>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M123" s="11" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr"/>
+      <c r="M123" s="11" t="inlineStr"/>
       <c r="N123" s="12" t="n">
         <v>0</v>
       </c>
@@ -9482,12 +9487,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
@@ -9497,7 +9502,7 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9515,28 +9520,28 @@
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
@@ -9552,12 +9557,12 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
@@ -9567,7 +9572,7 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9580,27 +9585,35 @@
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L125" s="11" t="inlineStr"/>
-      <c r="M125" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N125" s="12" t="n">
         <v>0</v>
       </c>
@@ -9614,12 +9627,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
@@ -9629,7 +9642,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9652,14 +9665,14 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>1.5</v>
+        <v>6.25</v>
       </c>
       <c r="L126" s="14" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -9676,22 +9689,22 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9699,44 +9712,36 @@
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M127" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L127" s="11" t="inlineStr"/>
+      <c r="M127" s="11" t="inlineStr"/>
       <c r="N127" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O127" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="12" t="n">
@@ -9746,22 +9751,22 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9769,7 +9774,7 @@
       </c>
       <c r="F128" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G128" s="14" t="inlineStr">
@@ -9779,12 +9784,12 @@
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
@@ -9795,16 +9800,16 @@
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N128" s="15" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O128" s="16" t="n">
         <v>0</v>
@@ -9816,22 +9821,22 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9844,7 +9849,7 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
@@ -9854,21 +9859,29 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L129" s="11" t="inlineStr"/>
-      <c r="M129" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L129" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M129" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N129" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O129" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P129" s="12" t="n">
@@ -9878,22 +9891,22 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -9916,25 +9929,17 @@
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K130" s="14" t="n">
         <v>2.5</v>
       </c>
-      <c r="L130" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M130" s="14" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+      <c r="L130" s="14" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
       <c r="N130" s="15" t="n">
         <v>0</v>
       </c>
@@ -9948,22 +9953,22 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -9986,17 +9991,25 @@
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L131" s="11" t="inlineStr"/>
-      <c r="M131" s="11" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L131" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M131" s="11" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N131" s="12" t="n">
         <v>0</v>
       </c>
@@ -10010,22 +10023,22 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10048,14 +10061,14 @@
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L132" s="14" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -10072,12 +10085,12 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
@@ -10087,7 +10100,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10100,7 +10113,7 @@
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
@@ -10110,25 +10123,17 @@
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L133" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M133" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr"/>
+      <c r="M133" s="11" t="inlineStr"/>
       <c r="N133" s="12" t="n">
         <v>0</v>
       </c>
@@ -10142,22 +10147,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10170,23 +10175,35 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H134" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H134" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L134" s="14" t="inlineStr"/>
-      <c r="M134" s="14" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L134" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M134" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N134" s="15" t="n">
         <v>0</v>
       </c>
@@ -10200,12 +10217,12 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
@@ -10215,7 +10232,7 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10231,32 +10248,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H135" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H135" s="11" t="inlineStr"/>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L135" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M135" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr"/>
+      <c r="M135" s="11" t="inlineStr"/>
       <c r="N135" s="12" t="n">
         <v>0</v>
       </c>
@@ -10270,12 +10275,12 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
@@ -10285,7 +10290,7 @@
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10308,17 +10313,25 @@
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L136" s="14" t="inlineStr"/>
-      <c r="M136" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L136" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M136" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N136" s="15" t="n">
         <v>0</v>
       </c>
@@ -10332,28 +10345,26 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E137" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="n">
+        <v/>
       </c>
       <c r="F137" s="11" t="inlineStr">
         <is>
@@ -10367,7 +10378,7 @@
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
@@ -10379,7 +10390,7 @@
         <v>35</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L137" s="11" t="inlineStr"/>
       <c r="M137" s="11" t="inlineStr"/>
@@ -10396,23 +10407,27 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C138" s="14" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C138" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F138" s="14" t="inlineStr">
@@ -10427,19 +10442,19 @@
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>8.5</v>
+        <v>1.25</v>
       </c>
       <c r="L138" s="14" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -10456,27 +10471,23 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C139" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr"/>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr">
@@ -10491,19 +10502,19 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="L139" s="11" t="inlineStr"/>
       <c r="M139" s="11" t="inlineStr"/>
@@ -10520,21 +10531,29 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C140" s="14" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C140" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E140" s="14" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10542,17 +10561,21 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H140" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H140" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K140" s="14" t="n">
         <v>0.5</v>
@@ -10572,18 +10595,18 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr"/>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr"/>
@@ -10600,14 +10623,14 @@
       <c r="H141" s="11" t="inlineStr"/>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L141" s="11" t="inlineStr"/>
       <c r="M141" s="11" t="inlineStr"/>
@@ -10624,18 +10647,18 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr"/>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr"/>
@@ -10646,56 +10669,48 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H142" s="14" t="inlineStr"/>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M142" s="14" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O142" s="15" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
       <c r="P142" s="15" t="n">
-        <v>1191.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr"/>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr"/>
@@ -10706,48 +10721,56 @@
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr"/>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr"/>
-      <c r="M143" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M143" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N143" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O143" s="12" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
       <c r="P143" s="12" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr"/>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E144" s="14" t="inlineStr"/>
@@ -10764,11 +10787,11 @@
       <c r="H144" s="14" t="inlineStr"/>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K144" s="14" t="n">
         <v>0.25</v>
@@ -10786,31 +10809,83 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="17" t="inlineStr">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr"/>
+      <c r="D145" s="11" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr"/>
+      <c r="F145" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr"/>
+      <c r="I145" s="11" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K145" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L145" s="11" t="inlineStr"/>
+      <c r="M145" s="11" t="inlineStr"/>
+      <c r="N145" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B145" s="17" t="inlineStr"/>
-      <c r="C145" s="17" t="inlineStr"/>
-      <c r="D145" s="17" t="inlineStr"/>
-      <c r="E145" s="17" t="inlineStr"/>
-      <c r="F145" s="17" t="inlineStr"/>
-      <c r="G145" s="17" t="inlineStr"/>
-      <c r="H145" s="17" t="inlineStr"/>
-      <c r="I145" s="17" t="inlineStr"/>
-      <c r="J145" s="17" t="inlineStr"/>
-      <c r="K145" s="17" t="inlineStr"/>
-      <c r="L145" s="17" t="inlineStr"/>
-      <c r="M145" s="17" t="inlineStr"/>
-      <c r="N145" s="18" t="n">
-        <v>62700.79400000001</v>
-      </c>
-      <c r="O145" s="18" t="n">
+      <c r="B146" s="17" t="inlineStr"/>
+      <c r="C146" s="17" t="inlineStr"/>
+      <c r="D146" s="17" t="inlineStr"/>
+      <c r="E146" s="17" t="inlineStr"/>
+      <c r="F146" s="17" t="inlineStr"/>
+      <c r="G146" s="17" t="inlineStr"/>
+      <c r="H146" s="17" t="inlineStr"/>
+      <c r="I146" s="17" t="inlineStr"/>
+      <c r="J146" s="17" t="inlineStr"/>
+      <c r="K146" s="17" t="inlineStr"/>
+      <c r="L146" s="17" t="inlineStr"/>
+      <c r="M146" s="17" t="inlineStr"/>
+      <c r="N146" s="18" t="n">
+        <v>63800.79400000001</v>
+      </c>
+      <c r="O146" s="18" t="n">
         <v>25875.837</v>
       </c>
-      <c r="P145" s="18" t="n">
-        <v>117.88</v>
+      <c r="P146" s="18" t="n">
+        <v>117.08</v>
       </c>
     </row>
   </sheetData>
@@ -10956,6 +11031,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11659,16 +11735,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>161.75</v>
+        <v>163</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>30.75</v>
+        <v>31</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>11.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>203.75</v>
+        <v>205.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>66.25</v>
@@ -11678,7 +11754,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.1%</t>
         </is>
       </c>
     </row>
@@ -12619,7 +12695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -12640,7 +12716,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7 clôture(s) : 7 projet(s), 0 rework</t>
+          <t>9 clôture(s) : 8 projet(s), 1 rework</t>
         </is>
       </c>
     </row>
@@ -12830,17 +12906,17 @@
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34848</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des a</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -12854,66 +12930,126 @@
         </is>
       </c>
       <c r="F10" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-34848</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE BRUAY LA BUISSIERE] - Modification en-tête des a</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-34966</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>[Commune de Villeneuve D'Ascq] - Ajout de 5 licences supplém</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Commune de Villeneuve D'Ascq</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Projet</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="F12" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>PDMDEP-14798</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>[CD Hauts-de-Seine]</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
-      <c r="F13" s="17" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n">
-        <v>0</v>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="28" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-08-26.xlsx
+++ b/jira_export_2026-08-26.xlsx
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>403 h</t>
+          <t>416 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -936,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P146"/>
+  <dimension ref="A1:P151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1168,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="L6" s="14" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
         <v>6</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>138.825</v>
       </c>
       <c r="P84" s="15" t="n">
-        <v>20.57</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="85">
@@ -8325,26 +8325,28 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E107" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
@@ -8363,29 +8365,29 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O107" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P107" s="12" t="n">
@@ -8395,28 +8397,26 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-25354</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Duncan HAMELIN</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E108" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>MAIRIE DE PLAN D'ORGON</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="n">
+        <v/>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
@@ -8435,23 +8435,23 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
@@ -8467,12 +8467,12 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
@@ -8482,13 +8482,11 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
-        </is>
-      </c>
-      <c r="E109" s="11" t="inlineStr">
-        <is>
-          <t>Script purge de données</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v/>
       </c>
       <c r="F109" s="11" t="inlineStr">
         <is>
@@ -8497,31 +8495,39 @@
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L109" s="11" t="inlineStr"/>
-      <c r="M109" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27017</t>
+        </is>
+      </c>
+      <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>00141205</t>
+        </is>
+      </c>
       <c r="N109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O109" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O109" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="12" t="n">
@@ -8531,12 +8537,12 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
@@ -8546,11 +8552,13 @@
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E110" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE SETE</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
@@ -8569,23 +8577,23 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27578</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>499043</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
@@ -8601,26 +8609,28 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
@@ -8629,35 +8639,27 @@
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L111" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27995</t>
-        </is>
-      </c>
-      <c r="M111" s="11" t="inlineStr">
-        <is>
-          <t>501218</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr"/>
+      <c r="M111" s="11" t="inlineStr"/>
       <c r="N111" s="12" t="n">
         <v>0</v>
       </c>
@@ -8671,22 +8673,22 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E112" s="14" t="n">
@@ -8709,23 +8711,23 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
@@ -8741,22 +8743,22 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8779,23 +8781,23 @@
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
@@ -8811,12 +8813,12 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
@@ -8826,7 +8828,7 @@
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8849,23 +8851,23 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>1.31</v>
+        <v>3</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
@@ -8881,12 +8883,12 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8896,7 +8898,7 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8919,23 +8921,23 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
         <v>13</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
@@ -8966,7 +8968,7 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -9000,12 +9002,12 @@
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
@@ -9070,12 +9072,12 @@
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
@@ -9091,22 +9093,22 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9124,34 +9126,34 @@
       </c>
       <c r="H118" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>0.5</v>
+        <v>1.31</v>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O118" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="15" t="n">
@@ -9161,12 +9163,12 @@
     <row r="119">
       <c r="A119" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
@@ -9176,7 +9178,7 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9192,20 +9194,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H119" s="11" t="inlineStr"/>
+      <c r="H119" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J119" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K119" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L119" s="11" t="inlineStr"/>
-      <c r="M119" s="11" t="inlineStr"/>
+        <v>1.31</v>
+      </c>
+      <c r="L119" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27365</t>
+        </is>
+      </c>
+      <c r="M119" s="11" t="inlineStr">
+        <is>
+          <t>491593</t>
+        </is>
+      </c>
       <c r="N119" s="12" t="n">
         <v>0</v>
       </c>
@@ -9219,12 +9233,12 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
@@ -9234,7 +9248,7 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9252,34 +9266,34 @@
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O120" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O120" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="15" t="n">
@@ -9289,12 +9303,12 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
@@ -9304,7 +9318,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9320,14 +9334,10 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H121" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H121" s="11" t="inlineStr"/>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
@@ -9336,16 +9346,8 @@
       <c r="K121" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L121" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28035</t>
-        </is>
-      </c>
-      <c r="M121" s="11" t="inlineStr">
-        <is>
-          <t>468660</t>
-        </is>
-      </c>
+      <c r="L121" s="11" t="inlineStr"/>
+      <c r="M121" s="11" t="inlineStr"/>
       <c r="N121" s="12" t="n">
         <v>0</v>
       </c>
@@ -9359,12 +9361,12 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
@@ -9374,7 +9376,7 @@
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9392,34 +9394,34 @@
       </c>
       <c r="H122" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
         <v>16</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O122" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="15" t="n">
@@ -9429,12 +9431,12 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
@@ -9444,7 +9446,7 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9457,23 +9459,35 @@
       </c>
       <c r="G123" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H123" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H123" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L123" s="11" t="inlineStr"/>
-      <c r="M123" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L123" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M123" s="11" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N123" s="12" t="n">
         <v>0</v>
       </c>
@@ -9487,12 +9501,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
@@ -9502,7 +9516,7 @@
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9520,34 +9534,34 @@
       </c>
       <c r="H124" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O124" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="15" t="n">
@@ -9557,22 +9571,22 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9585,35 +9599,23 @@
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H125" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr"/>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L125" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27568</t>
-        </is>
-      </c>
-      <c r="M125" s="11" t="inlineStr">
-        <is>
-          <t>471958</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr"/>
+      <c r="M125" s="11" t="inlineStr"/>
       <c r="N125" s="12" t="n">
         <v>0</v>
       </c>
@@ -9627,12 +9629,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
@@ -9642,7 +9644,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9655,7 +9657,7 @@
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H126" s="14" t="inlineStr">
@@ -9665,17 +9667,25 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L126" s="14" t="inlineStr"/>
-      <c r="M126" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L126" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M126" s="14" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N126" s="15" t="n">
         <v>0</v>
       </c>
@@ -9689,12 +9699,12 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
@@ -9704,7 +9714,7 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9717,27 +9727,35 @@
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L127" s="11" t="inlineStr"/>
-      <c r="M127" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N127" s="12" t="n">
         <v>0</v>
       </c>
@@ -9751,22 +9769,22 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9774,44 +9792,36 @@
       </c>
       <c r="F128" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M128" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>6.25</v>
+      </c>
+      <c r="L128" s="14" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
       <c r="N128" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O128" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P128" s="15" t="n">
@@ -9821,12 +9831,12 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -9836,7 +9846,7 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9849,39 +9859,31 @@
       </c>
       <c r="G129" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28023</t>
-        </is>
-      </c>
-      <c r="M129" s="11" t="inlineStr">
-        <is>
-          <t>454387</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L129" s="11" t="inlineStr"/>
+      <c r="M129" s="11" t="inlineStr"/>
       <c r="N129" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O129" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P129" s="12" t="n">
@@ -9891,22 +9893,22 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -9914,36 +9916,44 @@
       </c>
       <c r="F130" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H130" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L130" s="14" t="inlineStr"/>
-      <c r="M130" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L130" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M130" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N130" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O130" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="15" t="n">
@@ -9953,12 +9963,12 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
@@ -9968,7 +9978,7 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -9981,7 +9991,7 @@
       </c>
       <c r="G131" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
@@ -9991,23 +10001,23 @@
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>2.75</v>
+        <v>0.12</v>
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28003</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>412981</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
@@ -10023,22 +10033,22 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10051,7 +10061,7 @@
       </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H132" s="14" t="inlineStr">
@@ -10061,17 +10071,25 @@
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L132" s="14" t="inlineStr"/>
-      <c r="M132" s="14" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="L132" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M132" s="14" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N132" s="15" t="n">
         <v>0</v>
       </c>
@@ -10085,12 +10103,12 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
@@ -10100,7 +10118,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10113,7 +10131,7 @@
       </c>
       <c r="G133" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
@@ -10123,21 +10141,29 @@
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L133" s="11" t="inlineStr"/>
-      <c r="M133" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L133" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M133" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N133" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O133" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="12" t="n">
@@ -10147,22 +10173,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10175,7 +10201,7 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H134" s="14" t="inlineStr">
@@ -10185,25 +10211,17 @@
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L134" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M134" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L134" s="14" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
       <c r="N134" s="15" t="n">
         <v>0</v>
       </c>
@@ -10217,22 +10235,22 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10248,20 +10266,32 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H135" s="11" t="inlineStr"/>
+      <c r="H135" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L135" s="11" t="inlineStr"/>
-      <c r="M135" s="11" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N135" s="12" t="n">
         <v>0</v>
       </c>
@@ -10275,12 +10305,12 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
@@ -10290,7 +10320,7 @@
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10308,30 +10338,22 @@
       </c>
       <c r="H136" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L136" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M136" s="14" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L136" s="14" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
       <c r="N136" s="15" t="n">
         <v>0</v>
       </c>
@@ -10345,22 +10367,22 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10378,19 +10400,19 @@
       </c>
       <c r="H137" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L137" s="11" t="inlineStr"/>
       <c r="M137" s="11" t="inlineStr"/>
@@ -10407,12 +10429,12 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
@@ -10422,13 +10444,11 @@
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E138" s="14" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>[Arles]</t>
+        </is>
+      </c>
+      <c r="E138" s="14" t="n">
+        <v/>
       </c>
       <c r="F138" s="14" t="inlineStr">
         <is>
@@ -10442,19 +10462,19 @@
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="L138" s="14" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -10471,24 +10491,26 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C139" s="11" t="inlineStr"/>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E139" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="n">
+        <v/>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
@@ -10497,27 +10519,35 @@
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L139" s="11" t="inlineStr"/>
-      <c r="M139" s="11" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N139" s="12" t="n">
         <v>0</v>
       </c>
@@ -10531,12 +10561,12 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
@@ -10546,13 +10576,11 @@
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
-        </is>
-      </c>
-      <c r="E140" s="14" t="inlineStr">
-        <is>
-          <t>Montée de version + Pastell</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="n">
+        <v/>
       </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
@@ -10564,21 +10592,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H140" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H140" s="14" t="inlineStr"/>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L140" s="14" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -10595,21 +10619,27 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C141" s="11" t="inlineStr"/>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C141" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E141" s="11" t="inlineStr"/>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="n">
+        <v/>
+      </c>
       <c r="F141" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10617,23 +10647,35 @@
       </c>
       <c r="G141" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H141" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H141" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L141" s="11" t="inlineStr"/>
-      <c r="M141" s="11" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M141" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N141" s="12" t="n">
         <v>0</v>
       </c>
@@ -10647,21 +10689,27 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
-        </is>
-      </c>
-      <c r="C142" s="14" t="inlineStr"/>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C142" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
-        </is>
-      </c>
-      <c r="E142" s="14" t="inlineStr"/>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E142" s="14" t="n">
+        <v/>
+      </c>
       <c r="F142" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10669,20 +10717,24 @@
       </c>
       <c r="G142" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H142" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H142" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L142" s="14" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -10699,21 +10751,29 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C143" s="11" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C143" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E143" s="11" t="inlineStr"/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10721,59 +10781,59 @@
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H143" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H143" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M143" s="11" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr"/>
       <c r="N143" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O143" s="12" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
       <c r="P143" s="12" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr"/>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
-        </is>
-      </c>
-      <c r="E144" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E144" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F144" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10781,20 +10841,24 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H144" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H144" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>0.25</v>
+        <v>8.5</v>
       </c>
       <c r="L144" s="14" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -10811,21 +10875,29 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
-        </is>
-      </c>
-      <c r="C145" s="11" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
-        </is>
-      </c>
-      <c r="E145" s="11" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F145" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10833,20 +10905,24 @@
       </c>
       <c r="G145" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H145" s="11" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H145" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -10861,31 +10937,299 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="17" t="inlineStr">
+      <c r="A146" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1326</t>
+        </is>
+      </c>
+      <c r="B146" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr"/>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>MAIRIE DE SAINT-ISMIER</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="inlineStr"/>
+      <c r="F146" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G146" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H146" s="14" t="inlineStr"/>
+      <c r="I146" s="14" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="J146" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L146" s="14" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+      <c r="N146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>PSC-1320</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr"/>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>Commune de ETEL</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="inlineStr"/>
+      <c r="F147" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H147" s="11" t="inlineStr"/>
+      <c r="I147" s="11" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="J147" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K147" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L147" s="11" t="inlineStr"/>
+      <c r="M147" s="11" t="inlineStr"/>
+      <c r="N147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="inlineStr"/>
+      <c r="D148" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E148" s="14" t="inlineStr"/>
+      <c r="F148" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G148" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H148" s="14" t="inlineStr"/>
+      <c r="I148" s="14" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J148" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M148" s="14" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" s="15" t="n">
+        <v>595.7</v>
+      </c>
+      <c r="P148" s="15" t="n">
+        <v>595.7</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>PSC-850</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="C149" s="11" t="inlineStr"/>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>MAIRIE MARINGUES</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="inlineStr"/>
+      <c r="F149" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G149" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H149" s="11" t="inlineStr"/>
+      <c r="I149" s="11" t="inlineStr">
+        <is>
+          <t>10/06/2025</t>
+        </is>
+      </c>
+      <c r="J149" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="K149" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L149" s="11" t="inlineStr"/>
+      <c r="M149" s="11" t="inlineStr"/>
+      <c r="N149" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="13" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B150" s="14" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C150" s="14" t="inlineStr"/>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E150" s="14" t="inlineStr"/>
+      <c r="F150" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G150" s="14" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H150" s="14" t="inlineStr"/>
+      <c r="I150" s="14" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="n">
+        <v>17</v>
+      </c>
+      <c r="K150" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L150" s="14" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+      <c r="N150" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B146" s="17" t="inlineStr"/>
-      <c r="C146" s="17" t="inlineStr"/>
-      <c r="D146" s="17" t="inlineStr"/>
-      <c r="E146" s="17" t="inlineStr"/>
-      <c r="F146" s="17" t="inlineStr"/>
-      <c r="G146" s="17" t="inlineStr"/>
-      <c r="H146" s="17" t="inlineStr"/>
-      <c r="I146" s="17" t="inlineStr"/>
-      <c r="J146" s="17" t="inlineStr"/>
-      <c r="K146" s="17" t="inlineStr"/>
-      <c r="L146" s="17" t="inlineStr"/>
-      <c r="M146" s="17" t="inlineStr"/>
-      <c r="N146" s="18" t="n">
-        <v>63800.79400000001</v>
-      </c>
-      <c r="O146" s="18" t="n">
+      <c r="B151" s="17" t="inlineStr"/>
+      <c r="C151" s="17" t="inlineStr"/>
+      <c r="D151" s="17" t="inlineStr"/>
+      <c r="E151" s="17" t="inlineStr"/>
+      <c r="F151" s="17" t="inlineStr"/>
+      <c r="G151" s="17" t="inlineStr"/>
+      <c r="H151" s="17" t="inlineStr"/>
+      <c r="I151" s="17" t="inlineStr"/>
+      <c r="J151" s="17" t="inlineStr"/>
+      <c r="K151" s="17" t="inlineStr"/>
+      <c r="L151" s="17" t="inlineStr"/>
+      <c r="M151" s="17" t="inlineStr"/>
+      <c r="N151" s="18" t="n">
+        <v>63800.794</v>
+      </c>
+      <c r="O151" s="18" t="n">
         <v>25875.837</v>
       </c>
-      <c r="P146" s="18" t="n">
-        <v>117.08</v>
+      <c r="P151" s="18" t="n">
+        <v>114.75</v>
       </c>
     </row>
   </sheetData>
@@ -11032,6 +11376,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId146"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11735,26 +12084,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>163</v>
+        <v>166.75</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>31</v>
+        <v>31.25</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>11.25</v>
+        <v>11.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>205.25</v>
+        <v>209.75</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>66.25</v>
+        <v>69.25</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>601.65</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
     </row>
@@ -11796,7 +12145,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>108.25</v>
+        <v>113.75</v>
       </c>
     </row>
   </sheetData>
@@ -11884,13 +12233,13 @@
         <v>371498</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>139336</v>
+        <v>137636</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>232162</v>
+        <v>233862</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>145617</v>
+        <v>147317</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -11909,13 +12258,13 @@
         <v>163355</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>60505</v>
+        <v>58805</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>102851</v>
+        <v>104551</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>85660</v>
+        <v>87360</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>11307</v>

--- a/jira_export_2026-08-26.xlsx
+++ b/jira_export_2026-08-26.xlsx
@@ -818,21 +818,21 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>416 h</t>
+          <t>417 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>696 h</t>
+          <t>602 h</t>
         </is>
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -848,7 +848,7 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>851 h</t>
+          <t>736 h</t>
         </is>
       </c>
       <c r="B20" s="7" t="n"/>
@@ -936,7 +936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P151"/>
+  <dimension ref="A1:P152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -952,7 +952,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -2224,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
@@ -2961,32 +2961,32 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34126</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[SETE] - AME LiEx</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>AME LiEx</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
@@ -3008,22 +3008,22 @@
         <v>2</v>
       </c>
       <c r="K32" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34130</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>00170928</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>707</v>
-      </c>
-      <c r="O32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P32" s="15" t="n">
@@ -3033,12 +3033,12 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3068,64 +3068,64 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O33" s="16" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="P33" s="12" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34000</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Imprimante Bixolon</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Imprimante Bixolon</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
@@ -3145,36 +3145,44 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L34" s="14" t="inlineStr"/>
-      <c r="M34" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L34" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34070</t>
+        </is>
+      </c>
+      <c r="M34" s="14" t="inlineStr">
+        <is>
+          <t>00170468</t>
+        </is>
+      </c>
       <c r="N34" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="15" t="n">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>90</v>
       </c>
       <c r="P34" s="15" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34000</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE LA GARDE] - Imprimante Bixolon</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3184,12 +3192,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Imprimante Bixolon</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3199,12 +3207,12 @@
       </c>
       <c r="G35" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
@@ -3216,22 +3224,14 @@
         <v>2</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L35" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33991</t>
-        </is>
-      </c>
-      <c r="M35" s="11" t="inlineStr">
-        <is>
-          <t>00170408</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L35" s="11" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr"/>
       <c r="N35" s="12" t="n">
-        <v>510</v>
-      </c>
-      <c r="O35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P35" s="12" t="n">
@@ -3241,32 +3241,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3276,64 +3276,64 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>9.75</v>
+        <v>0.25</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>242.9</v>
-      </c>
-      <c r="O36" s="15" t="n">
-        <v>1118.61</v>
+        <v>510</v>
+      </c>
+      <c r="O36" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>114.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3360,57 +3360,57 @@
         <v>2</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.25</v>
+        <v>9.75</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>220</v>
-      </c>
-      <c r="O37" s="16" t="n">
-        <v>0</v>
+        <v>242.9</v>
+      </c>
+      <c r="O37" s="12" t="n">
+        <v>1118.61</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>0</v>
+        <v>114.73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
@@ -3436,18 +3436,18 @@
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="15" t="n">
+        <v>220</v>
+      </c>
+      <c r="O38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
@@ -3457,27 +3457,27 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3504,22 +3504,22 @@
         <v>2</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>680</v>
-      </c>
-      <c r="O39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
@@ -3529,32 +3529,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33822</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Installation serveurs et montée de version TEST ET PROD</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3564,49 +3564,49 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33833</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00169872</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="15" t="n">
-        <v>787.5</v>
+        <v>680</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P40" s="15" t="n">
-        <v>393.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33822</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[CD 29] - Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU FINISTERE (CD 29)</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>Installation serveurs et montée de version TEST ET PROD</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3648,37 +3648,37 @@
         <v>2</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>9.25</v>
+        <v>2</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33833</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00169872</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>438.2</v>
+        <v>787.5</v>
       </c>
       <c r="P41" s="12" t="n">
-        <v>47.37</v>
+        <v>393.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3720,52 +3720,52 @@
         <v>2</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O42" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O42" s="15" t="n">
+        <v>438.2</v>
       </c>
       <c r="P42" s="15" t="n">
-        <v>0</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3785,44 +3785,44 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="12" t="n">
-        <v>66.55</v>
+        <v>1890</v>
+      </c>
+      <c r="O43" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P43" s="12" t="n">
-        <v>133.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3857,64 +3857,64 @@
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>920</v>
+        <v>0</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>966</v>
+        <v>66.55</v>
       </c>
       <c r="P44" s="15" t="n">
-        <v>483</v>
+        <v>133.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33638</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOULINS</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier et MEP module Caisse</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3924,49 +3924,49 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33647</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00169251</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>3602.4</v>
-      </c>
-      <c r="O45" s="16" t="n">
-        <v>821.6</v>
+        <v>920</v>
+      </c>
+      <c r="O45" s="12" t="n">
+        <v>966</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>821.6</v>
+        <v>483</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33610</t>
+          <t>PDMDEP-33638</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
+          <t>[COMMUNE DE MOULINS] - Migration GEODP Placier + Acquisition module Caisse</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MORLAIX</t>
+          <t>COMMUNE DE MOULINS</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
+          <t>Migration GeODP Placier et MEP module Caisse</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4001,59 +4001,59 @@
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33616</t>
+          <t>PDMDEP-33647</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00169015</t>
+          <t>00169251</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>4040</v>
+        <v>3602.4</v>
       </c>
       <c r="O46" s="16" t="n">
-        <v>3535</v>
+        <v>821.6</v>
       </c>
       <c r="P46" s="15" t="n">
-        <v>1571.11</v>
+        <v>821.6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33610</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[COMMUNE DE MORLAIX] - Migration GEODP Placier hors matériel </t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>COMMUNE DE MORLAIX</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MIGRATION GEODP PLACIER hors matériel </t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -4080,52 +4080,52 @@
         <v>2</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33616</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169015</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1017.5</v>
+        <v>4040</v>
       </c>
       <c r="O47" s="16" t="n">
-        <v>691.9</v>
+        <v>3535</v>
       </c>
       <c r="P47" s="12" t="n">
-        <v>691.9</v>
+        <v>1571.11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4140,69 +4140,69 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>1416</v>
+        <v>1017.5</v>
       </c>
       <c r="O48" s="16" t="n">
-        <v>0</v>
+        <v>691.9</v>
       </c>
       <c r="P48" s="15" t="n">
-        <v>0</v>
+        <v>691.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4228,16 +4228,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>171.4</v>
+        <v>1416</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4249,32 +4249,32 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4300,16 +4300,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4321,32 +4321,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33386</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prestation modélisation Littéralis </t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4368,37 +4368,37 @@
         <v>3</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33390</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00167823</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>514.2</v>
-      </c>
-      <c r="O51" s="12" t="n">
-        <v>642.75</v>
+        <v>344</v>
+      </c>
+      <c r="O51" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>514.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33386</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT PIERRE DE LA REUNION] - Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>COMMUNE DE SAINT PIERRE DE LA REUNION</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t xml:space="preserve">Prestation modélisation Littéralis </t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4433,64 +4433,64 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33315</t>
+          <t>PDMDEP-33390</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00167138</t>
+          <t>00167823</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>0</v>
+        <v>514.2</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>224.76</v>
+        <v>642.75</v>
       </c>
       <c r="P52" s="15" t="n">
-        <v>0</v>
+        <v>514.2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4516,19 +4516,19 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33315</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167138</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="O53" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O53" s="12" t="n">
+        <v>224.76</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
@@ -4537,27 +4537,27 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
@@ -4588,16 +4588,16 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4609,32 +4609,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4644,38 +4644,38 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>8.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>625</v>
-      </c>
-      <c r="O55" s="12" t="n">
-        <v>945</v>
+        <v>149</v>
+      </c>
+      <c r="O55" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>112.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4732,53 +4732,53 @@
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>192</v>
+        <v>945</v>
       </c>
       <c r="P56" s="15" t="n">
-        <v>22.93</v>
+        <v>112.84</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4788,49 +4788,49 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>910</v>
+        <v>0</v>
       </c>
       <c r="O57" s="12" t="n">
-        <v>910</v>
+        <v>192</v>
       </c>
       <c r="P57" s="12" t="n">
-        <v>182</v>
+        <v>22.93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4865,59 +4865,59 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O58" s="16" t="n">
-        <v>0</v>
+        <v>910</v>
+      </c>
+      <c r="O58" s="15" t="n">
+        <v>910</v>
       </c>
       <c r="P58" s="15" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33012</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GRASSE</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP + Module Terrasse + formation sur site</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4937,64 +4937,64 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33021</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00165368</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="12" t="n">
-        <v>323.7</v>
+        <v>1207</v>
+      </c>
+      <c r="O59" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
-        <v>1294.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33012</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE GRASSE] - Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE GRASSE</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP + Module Terrasse + formation sur site</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5004,69 +5004,69 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33021</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165368</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="O60" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O60" s="15" t="n">
+        <v>323.7</v>
       </c>
       <c r="P60" s="15" t="n">
-        <v>0</v>
+        <v>1294.8</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
@@ -5088,20 +5088,20 @@
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O61" s="16" t="n">
         <v>0</v>
@@ -5113,12 +5113,12 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32950</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 1/2 (Pax + Mise en service)</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 1/2</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
@@ -5160,23 +5160,23 @@
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32958</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00165249</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="15" t="n">
-        <v>250</v>
+        <v>400</v>
+      </c>
+      <c r="O62" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P62" s="15" t="n">
         <v>0</v>
@@ -5185,32 +5185,32 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32950</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 1/2 (Pax + Mise en service)</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Migration GeODP Placier 1/2</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G63" s="11" t="inlineStr">
@@ -5220,35 +5220,35 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32958</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165249</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O63" s="12" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="P63" s="12" t="n">
         <v>0</v>
@@ -5257,12 +5257,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5297,44 +5297,44 @@
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>2.75</v>
+        <v>0.25</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>1294.224</v>
-      </c>
-      <c r="O64" s="16" t="n">
-        <v>219.36</v>
+        <v>0</v>
+      </c>
+      <c r="O64" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
-        <v>79.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32565</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>Afficher les AP signé avant MEP WFS</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H65" s="11" t="inlineStr">
@@ -5369,36 +5369,44 @@
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L65" s="11" t="inlineStr"/>
-      <c r="M65" s="11" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-32629</t>
+        </is>
+      </c>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
+          <t>00163182</t>
+        </is>
+      </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="12" t="n">
-        <v>0</v>
+        <v>1294.224</v>
+      </c>
+      <c r="O65" s="16" t="n">
+        <v>219.36</v>
       </c>
       <c r="P65" s="12" t="n">
-        <v>0</v>
+        <v>79.77</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5408,12 +5416,12 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5423,7 +5431,7 @@
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H66" s="14" t="inlineStr">
@@ -5440,22 +5448,14 @@
         <v>4</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-32556</t>
-        </is>
-      </c>
-      <c r="M66" s="14" t="inlineStr">
-        <is>
-          <t>00162313</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L66" s="14" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
       <c r="N66" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
@@ -5465,32 +5465,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5500,32 +5500,32 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K67" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5537,32 +5537,32 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
@@ -5572,34 +5572,34 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="15" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
@@ -5609,32 +5609,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5644,34 +5644,34 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O69" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5681,32 +5681,32 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -5716,65 +5716,69 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O70" s="16" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="P70" s="15" t="n">
-        <v>72.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C71" s="11" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -5784,64 +5788,60 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="O71" s="16" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="P71" s="12" t="n">
-        <v>0</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr"/>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5868,52 +5868,52 @@
         <v>5</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15" t="n">
-        <v>100</v>
+        <v>255</v>
+      </c>
+      <c r="O72" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5928,49 +5928,49 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O73" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
+        <v>100</v>
       </c>
       <c r="P73" s="12" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
@@ -6016,16 +6016,16 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>1000</v>
+        <v>590.15</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6037,32 +6037,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6072,69 +6072,69 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>11.75</v>
+        <v>0</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="12" t="n">
-        <v>109.972</v>
+        <v>1000</v>
+      </c>
+      <c r="O75" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
-        <v>9.359999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6144,69 +6144,69 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>285</v>
-      </c>
-      <c r="O76" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O76" s="15" t="n">
+        <v>109.972</v>
       </c>
       <c r="P76" s="15" t="n">
-        <v>0</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
@@ -6232,16 +6232,16 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6253,12 +6253,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
@@ -6304,16 +6304,16 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6325,32 +6325,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
@@ -6376,16 +6376,16 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O79" s="16" t="n">
         <v>0</v>
@@ -6397,27 +6397,27 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
@@ -6432,32 +6432,32 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K80" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O80" s="16" t="n">
         <v>0</v>
@@ -6469,12 +6469,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
@@ -6520,16 +6520,16 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O81" s="16" t="n">
         <v>0</v>
@@ -6541,32 +6541,32 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6576,49 +6576,49 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K82" s="14" t="n">
-        <v>12.25</v>
+        <v>0</v>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>700</v>
-      </c>
-      <c r="O82" s="15" t="n">
-        <v>1504.3</v>
+        <v>300</v>
+      </c>
+      <c r="O82" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P82" s="15" t="n">
-        <v>122.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
@@ -6628,12 +6628,12 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="G83" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
@@ -6660,44 +6660,52 @@
         <v>6</v>
       </c>
       <c r="K83" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L83" s="11" t="inlineStr"/>
-      <c r="M83" s="11" t="inlineStr"/>
+        <v>12.25</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N83" s="12" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="O83" s="12" t="n">
-        <v>0</v>
+        <v>1504.3</v>
       </c>
       <c r="P83" s="12" t="n">
-        <v>0</v>
+        <v>122.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
@@ -6707,7 +6715,7 @@
       </c>
       <c r="G84" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H84" s="14" t="inlineStr">
@@ -6717,64 +6725,56 @@
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K84" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L84" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M84" s="14" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L84" s="14" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
       <c r="N84" s="15" t="n">
-        <v>416.475</v>
-      </c>
-      <c r="O84" s="16" t="n">
-        <v>138.825</v>
+        <v>0</v>
+      </c>
+      <c r="O84" s="15" t="n">
+        <v>0</v>
       </c>
       <c r="P84" s="15" t="n">
-        <v>19.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6784,49 +6784,49 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J85" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K85" s="11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>210</v>
+        <v>416.475</v>
       </c>
       <c r="O85" s="16" t="n">
-        <v>0</v>
+        <v>138.825</v>
       </c>
       <c r="P85" s="12" t="n">
-        <v>0</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
@@ -6872,16 +6872,16 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="O86" s="16" t="n">
         <v>0</v>
@@ -6893,12 +6893,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
@@ -6944,16 +6944,16 @@
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="O87" s="16" t="n">
         <v>0</v>
@@ -6965,12 +6965,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
@@ -7016,16 +7016,16 @@
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O88" s="16" t="n">
         <v>0</v>
@@ -7037,12 +7037,12 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -7077,29 +7077,29 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" s="12" t="n">
+        <v>255</v>
+      </c>
+      <c r="O89" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P89" s="12" t="n">
@@ -7109,12 +7109,12 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
@@ -7149,29 +7149,29 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>140</v>
-      </c>
-      <c r="O90" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P90" s="15" t="n">
@@ -7181,32 +7181,32 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -7216,64 +7216,64 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O91" s="16" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
-        <v>26.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30044</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>CD29</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Commande du flux WFS COM pour Inforoute</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H92" s="14" t="inlineStr">
@@ -7293,44 +7293,44 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>1</v>
+        <v>8.75</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30046</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00153621</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" s="15" t="n">
-        <v>0</v>
+        <v>690</v>
+      </c>
+      <c r="O92" s="16" t="n">
+        <v>230</v>
       </c>
       <c r="P92" s="15" t="n">
-        <v>0</v>
+        <v>26.29</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-30044</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>[CD 29] - Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
@@ -7340,12 +7340,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>CD29</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Commande du flux WFS COM pour Inforoute</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="G93" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
@@ -7365,23 +7365,23 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K93" s="11" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-30046</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00153621</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
@@ -7397,12 +7397,12 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
@@ -7437,33 +7437,33 @@
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K94" s="14" t="n">
-        <v>2.42</v>
+        <v>0.25</v>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O94" s="15" t="n">
-        <v>224.05</v>
+        <v>0</v>
       </c>
       <c r="P94" s="15" t="n">
-        <v>92.70999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -7520,22 +7520,22 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O95" s="16" t="n">
-        <v>62.5</v>
+        <v>0</v>
+      </c>
+      <c r="O95" s="12" t="n">
+        <v>224.05</v>
       </c>
       <c r="P95" s="12" t="n">
-        <v>25.86</v>
+        <v>92.70999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -7592,47 +7592,49 @@
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O96" s="16" t="n">
-        <v>262.5</v>
+        <v>62.5</v>
       </c>
       <c r="P96" s="15" t="n">
-        <v>108.62</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E97" s="11" t="n">
-        <v/>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>Paramétrages complémentaires + Vision</t>
+        </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
@@ -7651,64 +7653,62 @@
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.5</v>
+        <v>2.42</v>
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="12" t="n">
-        <v>0</v>
+        <v>787.5</v>
+      </c>
+      <c r="O97" s="16" t="n">
+        <v>262.5</v>
       </c>
       <c r="P97" s="12" t="n">
-        <v>0</v>
+        <v>108.62</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E98" s="14" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE CARCASSONNE</t>
+        </is>
+      </c>
+      <c r="E98" s="14" t="n">
+        <v/>
       </c>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -7718,34 +7718,34 @@
       </c>
       <c r="H98" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>725</v>
-      </c>
-      <c r="O98" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P98" s="15" t="n">
@@ -7755,30 +7755,32 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E99" s="11" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -7788,49 +7790,49 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" s="12" t="n">
-        <v>1351.26</v>
+        <v>725</v>
+      </c>
+      <c r="O99" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
-        <v>675.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7840,13 +7842,11 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E100" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E100" s="14" t="n">
+        <v/>
       </c>
       <c r="F100" s="14" t="inlineStr">
         <is>
@@ -7865,33 +7865,33 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>1.05</v>
+        <v>2</v>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="15" t="n">
-        <v>0</v>
+        <v>1351.26</v>
       </c>
       <c r="P100" s="15" t="n">
-        <v>0</v>
+        <v>675.63</v>
       </c>
     </row>
     <row r="101">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
@@ -8020,12 +8020,12 @@
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
@@ -8164,18 +8164,18 @@
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8185,12 +8185,12 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
@@ -8200,11 +8200,13 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
@@ -8218,34 +8220,34 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>4.25</v>
+        <v>1.05</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O105" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8255,12 +8257,12 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
@@ -8270,7 +8272,7 @@
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8288,65 +8290,63 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>8.25</v>
+        <v>4.25</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O106" s="15" t="n">
-        <v>1280</v>
+        <v>0</v>
       </c>
       <c r="P106" s="15" t="n">
-        <v>155.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v/>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
@@ -8365,58 +8365,60 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>0.25</v>
+        <v>8.25</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O107" s="12" t="n">
-        <v>0</v>
+        <v>1280</v>
       </c>
       <c r="P107" s="12" t="n">
-        <v>0</v>
+        <v>155.15</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-25354</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Duncan HAMELIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE PLAN D'ORGON</t>
-        </is>
-      </c>
-      <c r="E108" s="14" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E108" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F108" s="14" t="inlineStr">
         <is>
@@ -8435,23 +8437,23 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>28/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26768</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00141775</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
@@ -8467,22 +8469,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-25354</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>Mairie de Plan d'Orgon  - Déploiement Littéralis Standard</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Duncan HAMELIN</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>MAIRIE DE PLAN D'ORGON</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8505,29 +8507,29 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>28/10/2025</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26768</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00141775</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O109" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="12" t="n">
@@ -8537,28 +8539,26 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E110" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E110" s="14" t="n">
+        <v/>
       </c>
       <c r="F110" s="14" t="inlineStr">
         <is>
@@ -8577,29 +8577,29 @@
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K110" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8609,27 +8609,27 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr">
@@ -8639,27 +8639,35 @@
       </c>
       <c r="G111" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="11" t="inlineStr"/>
-      <c r="M111" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N111" s="12" t="n">
         <v>0</v>
       </c>
@@ -8673,26 +8681,28 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E112" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
@@ -8701,35 +8711,27 @@
       </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H112" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L112" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M112" s="14" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L112" s="14" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
       <c r="N112" s="15" t="n">
         <v>0</v>
       </c>
@@ -8792,12 +8794,12 @@
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
@@ -8813,22 +8815,22 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8851,23 +8853,23 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
@@ -8883,12 +8885,12 @@
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8898,7 +8900,7 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8921,23 +8923,23 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.25</v>
+        <v>3</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
@@ -8953,12 +8955,12 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
@@ -8968,7 +8970,7 @@
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -8991,23 +8993,23 @@
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
         <v>13</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
@@ -9072,12 +9074,12 @@
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
@@ -9108,7 +9110,7 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9142,12 +9144,12 @@
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
@@ -9178,7 +9180,7 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -9212,12 +9214,12 @@
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
@@ -9233,22 +9235,22 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9266,34 +9268,34 @@
       </c>
       <c r="H120" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J120" s="14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K120" s="14" t="n">
-        <v>0.5</v>
+        <v>1.31</v>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O120" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P120" s="15" t="n">
@@ -9303,22 +9305,22 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9334,24 +9336,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H121" s="11" t="inlineStr"/>
+      <c r="H121" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J121" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K121" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L121" s="11" t="inlineStr"/>
-      <c r="M121" s="11" t="inlineStr"/>
+      <c r="L121" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M121" s="11" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O121" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P121" s="12" t="n">
@@ -9361,22 +9375,22 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9392,11 +9406,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H122" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H122" s="14" t="inlineStr"/>
       <c r="I122" s="14" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -9406,18 +9416,10 @@
         <v>16</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="L122" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M122" s="14" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L122" s="14" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
       <c r="N122" s="15" t="n">
         <v>0</v>
       </c>
@@ -9431,22 +9433,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9464,28 +9466,28 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K123" s="11" t="n">
-        <v>0.5</v>
+        <v>7</v>
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
@@ -9501,22 +9503,22 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9539,29 +9541,29 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
         <v>16</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O124" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="15" t="n">
@@ -9571,22 +9573,22 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9599,27 +9601,39 @@
       </c>
       <c r="G125" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H125" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H125" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L125" s="11" t="inlineStr"/>
-      <c r="M125" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L125" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M125" s="11" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N125" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O125" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="12" t="n">
@@ -9629,22 +9643,22 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9657,35 +9671,23 @@
       </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H126" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H126" s="14" t="inlineStr"/>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K126" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L126" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M126" s="14" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L126" s="14" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
       <c r="N126" s="15" t="n">
         <v>0</v>
       </c>
@@ -9699,12 +9701,12 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
@@ -9714,7 +9716,7 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -9732,28 +9734,28 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N127" s="12" t="n">
@@ -9769,12 +9771,12 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
@@ -9784,7 +9786,7 @@
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E128" s="14" t="n">
@@ -9797,27 +9799,35 @@
       </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H128" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K128" s="14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L128" s="14" t="inlineStr"/>
-      <c r="M128" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L128" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27568</t>
+        </is>
+      </c>
+      <c r="M128" s="14" t="inlineStr">
+        <is>
+          <t>471958</t>
+        </is>
+      </c>
       <c r="N128" s="15" t="n">
         <v>0</v>
       </c>
@@ -9831,12 +9841,12 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
@@ -9846,7 +9856,7 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9869,14 +9879,14 @@
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J129" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>1.5</v>
+        <v>6.25</v>
       </c>
       <c r="L129" s="11" t="inlineStr"/>
       <c r="M129" s="11" t="inlineStr"/>
@@ -9893,22 +9903,22 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -9916,44 +9926,36 @@
       </c>
       <c r="F130" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H130" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M130" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L130" s="14" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
       <c r="N130" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O130" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="15" t="n">
@@ -9963,22 +9965,22 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -9986,7 +9988,7 @@
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
@@ -9996,34 +9998,34 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O131" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P131" s="12" t="n">
@@ -10048,7 +10050,7 @@
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10082,7 +10084,7 @@
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M132" s="14" t="inlineStr">
@@ -10103,12 +10105,12 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
@@ -10118,7 +10120,7 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10148,22 +10150,22 @@
         <v>20</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M133" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N133" s="12" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O133" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="12" t="n">
@@ -10173,22 +10175,22 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10201,7 +10203,7 @@
       </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H134" s="14" t="inlineStr">
@@ -10211,21 +10213,29 @@
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L134" s="14" t="inlineStr"/>
-      <c r="M134" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L134" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M134" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N134" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O134" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P134" s="15" t="n">
@@ -10235,22 +10245,22 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10273,25 +10283,17 @@
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L135" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M135" s="11" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr"/>
+      <c r="M135" s="11" t="inlineStr"/>
       <c r="N135" s="12" t="n">
         <v>0</v>
       </c>
@@ -10305,22 +10307,22 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10343,17 +10345,25 @@
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K136" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L136" s="14" t="inlineStr"/>
-      <c r="M136" s="14" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L136" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M136" s="14" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N136" s="15" t="n">
         <v>0</v>
       </c>
@@ -10367,22 +10377,22 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10405,14 +10415,14 @@
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L137" s="11" t="inlineStr"/>
       <c r="M137" s="11" t="inlineStr"/>
@@ -10429,12 +10439,12 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
@@ -10444,7 +10454,7 @@
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10462,19 +10472,19 @@
       </c>
       <c r="H138" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
         <v>33</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L138" s="14" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -10491,12 +10501,12 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
@@ -10506,7 +10516,7 @@
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -10519,35 +10529,27 @@
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K139" s="11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L139" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M139" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L139" s="11" t="inlineStr"/>
+      <c r="M139" s="11" t="inlineStr"/>
       <c r="N139" s="12" t="n">
         <v>0</v>
       </c>
@@ -10561,22 +10563,22 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E140" s="14" t="n">
@@ -10589,23 +10591,35 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H140" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H140" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" s="14" t="inlineStr"/>
-      <c r="M140" s="14" t="inlineStr"/>
+        <v>2.25</v>
+      </c>
+      <c r="L140" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M140" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N140" s="15" t="n">
         <v>0</v>
       </c>
@@ -10619,12 +10633,12 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
@@ -10634,7 +10648,7 @@
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -10650,32 +10664,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H141" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H141" s="11" t="inlineStr"/>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K141" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L141" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M141" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L141" s="11" t="inlineStr"/>
+      <c r="M141" s="11" t="inlineStr"/>
       <c r="N141" s="12" t="n">
         <v>0</v>
       </c>
@@ -10689,12 +10691,12 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr">
@@ -10704,7 +10706,7 @@
       </c>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E142" s="14" t="n">
@@ -10727,17 +10729,25 @@
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K142" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L142" s="14" t="inlineStr"/>
-      <c r="M142" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L142" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M142" s="14" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N142" s="15" t="n">
         <v>0</v>
       </c>
@@ -10751,28 +10761,26 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E143" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="n">
+        <v/>
       </c>
       <c r="F143" s="11" t="inlineStr">
         <is>
@@ -10786,7 +10794,7 @@
       </c>
       <c r="H143" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
@@ -10798,7 +10806,7 @@
         <v>35</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="L143" s="11" t="inlineStr"/>
       <c r="M143" s="11" t="inlineStr"/>
@@ -10815,23 +10823,27 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C144" s="14" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C144" s="14" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F144" s="14" t="inlineStr">
@@ -10846,19 +10858,19 @@
       </c>
       <c r="H144" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>8.5</v>
+        <v>1.25</v>
       </c>
       <c r="L144" s="14" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -10875,27 +10887,23 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-2155</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
-        </is>
-      </c>
-      <c r="C145" s="11" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C145" s="11" t="inlineStr"/>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>Montée de version + Pastell</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr">
@@ -10910,19 +10918,19 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>02/08/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>0.5</v>
+        <v>8.5</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -10939,21 +10947,29 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PDMDEP-2155</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="C146" s="14" t="inlineStr"/>
+          <t>[CHAMBERY] Montée de version Test et Prod + PASTELL</t>
+        </is>
+      </c>
+      <c r="C146" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
-        </is>
-      </c>
-      <c r="E146" s="14" t="inlineStr"/>
+          <t>COMMUNE DE CHAMBERY</t>
+        </is>
+      </c>
+      <c r="E146" s="14" t="inlineStr">
+        <is>
+          <t>Montée de version + Pastell</t>
+        </is>
+      </c>
       <c r="F146" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10961,17 +10977,21 @@
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H146" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H146" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>02/08/2023</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K146" s="14" t="n">
         <v>0.5</v>
@@ -10991,18 +11011,18 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr"/>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr"/>
@@ -11019,14 +11039,14 @@
       <c r="H147" s="11" t="inlineStr"/>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J147" s="11" t="n">
         <v>1</v>
       </c>
       <c r="K147" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L147" s="11" t="inlineStr"/>
       <c r="M147" s="11" t="inlineStr"/>
@@ -11043,18 +11063,18 @@
     <row r="148">
       <c r="A148" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B148" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C148" s="14" t="inlineStr"/>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E148" s="14" t="inlineStr"/>
@@ -11065,56 +11085,48 @@
       </c>
       <c r="G148" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H148" s="14" t="inlineStr"/>
       <c r="I148" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J148" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K148" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L148" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M148" s="14" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L148" s="14" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
       <c r="N148" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O148" s="15" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
       <c r="P148" s="15" t="n">
-        <v>595.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="10" t="inlineStr">
         <is>
-          <t>PSC-850</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr"/>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE MARINGUES</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr"/>
@@ -11125,48 +11137,56 @@
       </c>
       <c r="G149" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr"/>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>10/06/2025</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J149" s="11" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="K149" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L149" s="11" t="inlineStr"/>
-      <c r="M149" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L149" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M149" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N149" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O149" s="12" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
       <c r="P149" s="12" t="n">
-        <v>0</v>
+        <v>595.7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>PSC-583</t>
+          <t>PSC-850</t>
         </is>
       </c>
       <c r="B150" s="14" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="C150" s="14" t="inlineStr"/>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>Cournonsec</t>
+          <t>MAIRIE MARINGUES</t>
         </is>
       </c>
       <c r="E150" s="14" t="inlineStr"/>
@@ -11183,11 +11203,11 @@
       <c r="H150" s="14" t="inlineStr"/>
       <c r="I150" s="14" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>10/06/2025</t>
         </is>
       </c>
       <c r="J150" s="14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K150" s="14" t="n">
         <v>0.25</v>
@@ -11205,31 +11225,83 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="17" t="inlineStr">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>PSC-583</t>
+        </is>
+      </c>
+      <c r="B151" s="11" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="C151" s="11" t="inlineStr"/>
+      <c r="D151" s="11" t="inlineStr">
+        <is>
+          <t>Cournonsec</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="inlineStr"/>
+      <c r="F151" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H151" s="11" t="inlineStr"/>
+      <c r="I151" s="11" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J151" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="K151" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L151" s="11" t="inlineStr"/>
+      <c r="M151" s="11" t="inlineStr"/>
+      <c r="N151" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B151" s="17" t="inlineStr"/>
-      <c r="C151" s="17" t="inlineStr"/>
-      <c r="D151" s="17" t="inlineStr"/>
-      <c r="E151" s="17" t="inlineStr"/>
-      <c r="F151" s="17" t="inlineStr"/>
-      <c r="G151" s="17" t="inlineStr"/>
-      <c r="H151" s="17" t="inlineStr"/>
-      <c r="I151" s="17" t="inlineStr"/>
-      <c r="J151" s="17" t="inlineStr"/>
-      <c r="K151" s="17" t="inlineStr"/>
-      <c r="L151" s="17" t="inlineStr"/>
-      <c r="M151" s="17" t="inlineStr"/>
-      <c r="N151" s="18" t="n">
-        <v>63800.794</v>
-      </c>
-      <c r="O151" s="18" t="n">
+      <c r="B152" s="17" t="inlineStr"/>
+      <c r="C152" s="17" t="inlineStr"/>
+      <c r="D152" s="17" t="inlineStr"/>
+      <c r="E152" s="17" t="inlineStr"/>
+      <c r="F152" s="17" t="inlineStr"/>
+      <c r="G152" s="17" t="inlineStr"/>
+      <c r="H152" s="17" t="inlineStr"/>
+      <c r="I152" s="17" t="inlineStr"/>
+      <c r="J152" s="17" t="inlineStr"/>
+      <c r="K152" s="17" t="inlineStr"/>
+      <c r="L152" s="17" t="inlineStr"/>
+      <c r="M152" s="17" t="inlineStr"/>
+      <c r="N152" s="18" t="n">
+        <v>63800.79399999999</v>
+      </c>
+      <c r="O152" s="18" t="n">
         <v>25875.837</v>
       </c>
-      <c r="P151" s="18" t="n">
-        <v>114.75</v>
+      <c r="P152" s="18" t="n">
+        <v>114.49</v>
       </c>
     </row>
   </sheetData>
@@ -11381,6 +11453,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11700,7 +11773,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>146 j</t>
+          <t>128 j</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11785,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>851 h</t>
+          <t>736 h</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11826,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>330.75</v>
+        <v>280.88</v>
       </c>
     </row>
     <row r="14">
@@ -11768,7 +11841,7 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>88.2</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -11783,7 +11856,7 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>22.05</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="16"/>
@@ -11823,7 +11896,7 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>103.74</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="20">
@@ -11853,7 +11926,7 @@
         </is>
       </c>
       <c r="C21" s="11" t="n">
-        <v>5.46</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="22"/>
@@ -11893,7 +11966,7 @@
         </is>
       </c>
       <c r="C25" s="11" t="n">
-        <v>270.9</v>
+        <v>252</v>
       </c>
     </row>
     <row r="26">
@@ -11923,7 +11996,7 @@
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>30.1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28"/>
@@ -11963,7 +12036,7 @@
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>705.39</v>
+        <v>610.01</v>
       </c>
     </row>
     <row r="32">
@@ -11978,7 +12051,7 @@
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>88.2</v>
+        <v>74.90000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -11993,7 +12066,7 @@
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>57.61</v>
+        <v>50.79</v>
       </c>
     </row>
   </sheetData>
@@ -12084,7 +12157,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>166.75</v>
+        <v>167.25</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>31.25</v>
@@ -12093,17 +12166,17 @@
         <v>11.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>209.75</v>
+        <v>210.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>69.25</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>601.65</v>
+        <v>532.88</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>39.5%</t>
         </is>
       </c>
     </row>
@@ -12129,11 +12202,11 @@
         <v>6.5</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>103.74</v>
+        <v>77.14</v>
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>20.4%</t>
         </is>
       </c>
     </row>
